--- a/output/pdf_financials_xlsx/EPIC.xlsx
+++ b/output/pdf_financials_xlsx/EPIC.xlsx
@@ -583,7 +583,7 @@
         <v>10.458285</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>9.263498</v>
+        <v>14.748698</v>
       </c>
     </row>
     <row r="11">
@@ -599,7 +599,7 @@
         <v>0.724794</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.199048</v>
+        <v>0.713848</v>
       </c>
     </row>
     <row r="12">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.079183</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.968699</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.479746</v>
       </c>
     </row>
     <row r="35">
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.079183</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.968699</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.669799</v>
+        <v>6.149545</v>
       </c>
     </row>
     <row r="37">
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.21577</v>
+        <v>1.136587</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>7.145075</v>
+        <v>2.176376</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>32.168591</v>
+        <v>26.688845</v>
       </c>
     </row>
     <row r="49">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6447,7 +6447,11 @@
           <t>Interest expense (Note 9 (a), (c))</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="n">
         <v>0.277072</v>
       </c>

--- a/output/pdf_financials_xlsx/EPIC.xlsx
+++ b/output/pdf_financials_xlsx/EPIC.xlsx
@@ -887,13 +887,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.646724</v>
+        <v>0.5048</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.767014</v>
+        <v>0.497876</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.685125</v>
+        <v>0.431007</v>
       </c>
     </row>
     <row r="29">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.694314</v>
+        <v>-0.836238</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.245203</v>
+        <v>0.976065</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.673295</v>
+        <v>0.419177</v>
       </c>
     </row>
     <row r="30">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1.964588879230728</v>
+        <v>-2.366168441353833</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2.176054057722019</v>
+        <v>1.70572204198869</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.9176919607283806</v>
+        <v>0.571332570451645</v>
       </c>
     </row>
     <row r="31">
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.5048</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.497876</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.431007</v>
       </c>
     </row>
     <row r="101">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -4526,7 +4526,11 @@
           <t>Additions to intangible assets (Note 6, 16)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -5328,7 +5332,11 @@
           <t>Additions to intangible assets (Note 15)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>-0.6181</v>
       </c>
@@ -5746,7 +5754,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">

--- a/output/pdf_financials_xlsx/EPIC.xlsx
+++ b/output/pdf_financials_xlsx/EPIC.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-1.341038</v>
+        <v>-1.475616</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.478189</v>
+        <v>1.3407</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.01183</v>
+        <v>1.198697</v>
       </c>
     </row>
     <row r="17">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.427181</v>
+        <v>0.561759</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.137717</v>
+        <v>-0.724794</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.496679</v>
+        <v>-0.713848</v>
       </c>
     </row>
     <row r="18">
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.341038</v>
+        <v>-1.475616</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.478189</v>
+        <v>1.3407</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.01183</v>
+        <v>1.198697</v>
       </c>
     </row>
     <row r="28">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.836238</v>
+        <v>-0.970816</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.976065</v>
+        <v>1.838576</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.419177</v>
+        <v>1.629704</v>
       </c>
     </row>
     <row r="30">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-2.366168441353833</v>
+        <v>-2.746962206406983</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1.70572204198869</v>
+        <v>3.21300283185177</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.571332570451645</v>
+        <v>2.221264466789274</v>
       </c>
     </row>
     <row r="31">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-31.85450375008016</v>
+        <v>-38.06945709452866</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>28.79970053681703</v>
+        <v>54.06086372790333</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-4198.469991546915</v>
+        <v>59.55199687660851</v>
       </c>
     </row>
     <row r="32">
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.565963</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.180401</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.051342</v>
       </c>
     </row>
     <row r="111">
@@ -3321,7 +3321,11 @@
           <t>Lease liabilities (Note 7)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -3765,7 +3769,11 @@
           <t>Lease liabilities (Note 9 (d))</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>4.147161</v>
       </c>
@@ -4067,7 +4075,11 @@
           <t>Accretion (Note 9)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4127,7 +4139,11 @@
           <t>Deferred tax recovery (Note 19)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -4396,7 +4412,11 @@
           <t>Proceeds from private placement (Note 10(a))</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>5.8</v>
       </c>
@@ -4805,7 +4825,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>-0.913857</v>
       </c>
@@ -4863,7 +4887,11 @@
           <t>Accretion (Note 9 (a), (c))</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>0.565963</v>
       </c>
@@ -4921,7 +4949,11 @@
           <t>Deferred tax recovery (Note 18)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>-0.075083</v>
       </c>
@@ -5998,7 +6030,11 @@
           <t>Income before income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -6616,7 +6652,11 @@
           <t>Income (loss) before income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>-0.561759</v>
       </c>
